--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/ValFundMarketInfo001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/ValFundMarketInfo001.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>基金代码</t>
   </si>
@@ -43,11 +43,7 @@
     <t>卖一价</t>
   </si>
   <si>
-    <t>估值日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剩余期限</t>
+    <t>估值日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -368,13 +364,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -388,24 +384,21 @@
         <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
         <v>8</v>
       </c>
     </row>
